--- a/hira_material_automation/output/monthly/202601_202608__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-04T22:46:53</t>
+          <t>2026-08-14T21:59:02</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d72954c2090e709d66bf78f05a767bffbb08adb3a81cb9eef604f4ad6d7128ac</t>
+          <t>68f85d541b48c71060f83e154dee085979651efa125b32f59bb1cafa98df6319</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202608__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202608__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-14T21:59:02</t>
+          <t>2026-08-24T22:04:06</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>68f85d541b48c71060f83e154dee085979651efa125b32f59bb1cafa98df6319</t>
+          <t>3228e2a8e67a703ddd70844851fd664413d9952635211faa0b990e85bf8a2102</t>
         </is>
       </c>
     </row>
